--- a/seeds/DATA_PEGAWAI_BID_PEMASARAN.xlsx
+++ b/seeds/DATA_PEGAWAI_BID_PEMASARAN.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="update" sheetId="1" r:id="R691fa3256e8a4af7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy of Sheet1" sheetId="2" r:id="R304baa2ffe204f71"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="update" sheetId="1" r:id="Rc2afccab28b044c3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Copy of Sheet1" sheetId="2" r:id="Ra33aecc42dc54975"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -66,9 +66,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">CHANDRA NURHIDAYAT., S.Hub.,Int.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">Penata (III/c)</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">198810202014031004</x:t>
@@ -969,14 +966,14 @@
       <x:c r="D7" s="8" t="s">
         <x:v>15</x:v>
       </x:c>
-      <x:c r="E7" s="8" t="s">
+      <x:c r="E7" s="8" t="str">
+        <x:v>Penata Tk. I (III/d)</x:v>
+      </x:c>
+      <x:c r="F7" s="8" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="F7" s="8" t="s">
+      <x:c r="G7" s="11" t="s">
         <x:v>20</x:v>
-      </x:c>
-      <x:c r="G7" s="11" t="s">
-        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -984,19 +981,19 @@
         <x:v>4.0</x:v>
       </x:c>
       <x:c r="B8" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="7" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D8" s="8" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="s">
         <x:v>23</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="s">
+      <x:c r="F8" s="6" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="F8" s="6" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1004,19 +1001,19 @@
         <x:v>5.0</x:v>
       </x:c>
       <x:c r="B9" s="12" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D9" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E9" s="8" t="s">
         <x:v>16</x:v>
       </x:c>
       <x:c r="F9" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1024,19 +1021,19 @@
         <x:v>6.0</x:v>
       </x:c>
       <x:c r="B10" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D10" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="E10" s="8" t="str">
         <x:v>Penata Tk. I (III/d)</x:v>
       </x:c>
       <x:c r="F10" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1044,19 +1041,19 @@
         <x:v>7.0</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C11" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D11" s="6" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="s">
         <x:v>32</x:v>
-      </x:c>
-      <x:c r="E11" s="6" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F11" s="6" t="s">
-        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1064,19 +1061,19 @@
         <x:v>8.0</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>34</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C12" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D12" s="6" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="s">
+      <x:c r="F12" s="6" t="s">
         <x:v>36</x:v>
-      </x:c>
-      <x:c r="F12" s="6" t="s">
-        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1084,19 +1081,19 @@
         <x:v>9.0</x:v>
       </x:c>
       <x:c r="B13" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C13" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D13" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E13" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F13" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1104,19 +1101,19 @@
         <x:v>10.0</x:v>
       </x:c>
       <x:c r="B14" s="6" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C14" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D14" s="6" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E14" s="6" t="s">
+      <x:c r="F14" s="6" t="s">
         <x:v>42</x:v>
-      </x:c>
-      <x:c r="F14" s="6" t="s">
-        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1124,19 +1121,19 @@
         <x:v>11.0</x:v>
       </x:c>
       <x:c r="B15" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C15" s="7" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D15" s="8" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E15" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F15" s="13" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1144,19 +1141,19 @@
         <x:v>12.0</x:v>
       </x:c>
       <x:c r="B16" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C16" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D16" s="6" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="E16" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F16" s="6" t="s">
         <x:v>47</x:v>
-      </x:c>
-      <x:c r="E16" s="6" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F16" s="6" t="s">
-        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1164,19 +1161,19 @@
         <x:v>13.0</x:v>
       </x:c>
       <x:c r="B17" s="6" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D17" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E17" s="6" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F17" s="6" t="s">
         <x:v>50</x:v>
-      </x:c>
-      <x:c r="E17" s="6" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="F17" s="6" t="s">
-        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1184,19 +1181,19 @@
         <x:v>14.0</x:v>
       </x:c>
       <x:c r="B18" s="6" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C18" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D18" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E18" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F18" s="6" t="s">
-        <x:v>53</x:v>
+        <x:v>52</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1204,19 +1201,19 @@
         <x:v>15.0</x:v>
       </x:c>
       <x:c r="B19" s="6" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C19" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D19" s="6" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E19" s="6" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E19" s="6" t="s">
+      <x:c r="F19" s="6" t="s">
         <x:v>56</x:v>
-      </x:c>
-      <x:c r="F19" s="6" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1224,19 +1221,19 @@
         <x:v>16.0</x:v>
       </x:c>
       <x:c r="B20" s="6" t="s">
-        <x:v>58</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D20" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E20" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F20" s="6" t="s">
-        <x:v>59</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1244,19 +1241,19 @@
         <x:v>17.0</x:v>
       </x:c>
       <x:c r="B21" s="6" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C21" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D21" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E21" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F21" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1264,19 +1261,19 @@
         <x:v>18.0</x:v>
       </x:c>
       <x:c r="B22" s="6" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D22" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E22" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F22" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1284,19 +1281,19 @@
         <x:v>19.0</x:v>
       </x:c>
       <x:c r="B23" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D23" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E23" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F23" s="6" t="s">
-        <x:v>65</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1304,19 +1301,19 @@
         <x:v>20.0</x:v>
       </x:c>
       <x:c r="B24" s="6" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C24" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D24" s="6" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E24" s="6" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="E24" s="6" t="s">
+      <x:c r="F24" s="6" t="s">
         <x:v>68</x:v>
-      </x:c>
-      <x:c r="F24" s="6" t="s">
-        <x:v>69</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1324,19 +1321,19 @@
         <x:v>21.0</x:v>
       </x:c>
       <x:c r="B25" s="15" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C25" s="16" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D25" s="15" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E25" s="15" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="E25" s="15" t="s">
-        <x:v>68</x:v>
-      </x:c>
       <x:c r="F25" s="15" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -1388,7 +1385,7 @@
     </x:row>
     <x:row r="32">
       <x:c r="B32" s="6" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C32" s="10" t="s">
         <x:v>9</x:v>
@@ -1400,24 +1397,24 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="F32" s="6" t="s">
-        <x:v>72</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="B33" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C33" s="10" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="D33" s="6" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E33" s="6" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E33" s="6" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="F33" s="6" t="s">
-        <x:v>74</x:v>
+        <x:v>73</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -1425,19 +1422,19 @@
         <x:v>2.0</x:v>
       </x:c>
       <x:c r="B34" s="6" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C34" s="10" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="D34" s="6" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E34" s="9" t="s">
         <x:v>11</x:v>
       </x:c>
       <x:c r="F34" s="6" t="s">
-        <x:v>77</x:v>
+        <x:v>76</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1493,22 +1490,22 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B4" s="22" t="s">
-        <x:v>78</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C4" s="22" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="23" t="s">
-        <x:v>79</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E4" s="22" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="F4" s="22" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G4" s="22" t="s">
         <x:v>80</x:v>
-      </x:c>
-      <x:c r="G4" s="22" t="s">
-        <x:v>81</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1522,16 +1519,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="D5" s="6" t="s">
-        <x:v>82</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="E5" s="8" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="F5" s="24" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G5" s="9" t="s">
         <x:v>83</x:v>
-      </x:c>
-      <x:c r="G5" s="9" t="s">
-        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="6">
@@ -1542,19 +1539,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C6" s="6" t="s">
-        <x:v>75</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D6" s="25">
         <x:v>40422.0</x:v>
       </x:c>
       <x:c r="E6" s="6" t="s">
-        <x:v>76</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F6" s="24" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="s">
         <x:v>85</x:v>
-      </x:c>
-      <x:c r="G6" s="6" t="s">
-        <x:v>86</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1574,10 +1571,10 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="F7" s="24" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="s">
         <x:v>87</x:v>
-      </x:c>
-      <x:c r="G7" s="6" t="s">
-        <x:v>88</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1588,19 +1585,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C8" s="6" t="s">
-        <x:v>71</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D8" s="6" t="s">
-        <x:v>89</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E8" s="6" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F8" s="24" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="s">
         <x:v>90</x:v>
-      </x:c>
-      <x:c r="G8" s="6" t="s">
-        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1614,19 +1611,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="D9" s="6" t="s">
-        <x:v>92</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E9" s="8" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="F9" s="24" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="G9" s="8" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="G9" s="8" t="s">
-        <x:v>94</x:v>
-      </x:c>
       <x:c r="H9" s="11" t="s">
-        <x:v>21</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1637,19 +1634,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="6" t="s">
-        <x:v>95</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D10" s="26">
         <x:v>36617.0</x:v>
       </x:c>
       <x:c r="E10" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F10" s="24" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="G10" s="6" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="G10" s="6" t="s">
-        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1660,19 +1657,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C11" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D11" s="6" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="F11" s="24" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="E11" s="6" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="F11" s="24" t="s">
+      <x:c r="G11" s="6" t="s">
         <x:v>99</x:v>
-      </x:c>
-      <x:c r="G11" s="6" t="s">
-        <x:v>100</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1683,19 +1680,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D12" s="6" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E12" s="8" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="E12" s="8" t="s">
+      <x:c r="F12" s="24" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="F12" s="24" t="s">
+      <x:c r="G12" s="6" t="s">
         <x:v>103</x:v>
-      </x:c>
-      <x:c r="G12" s="6" t="s">
-        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1706,19 +1703,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C13" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D13" s="26">
         <x:v>44166.0</x:v>
       </x:c>
       <x:c r="E13" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F13" s="24" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="s">
         <x:v>105</x:v>
-      </x:c>
-      <x:c r="G13" s="6" t="s">
-        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1729,19 +1726,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C14" s="6" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="D14" s="27" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D14" s="27" t="s">
+      <x:c r="F14" s="24" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="E14" s="6" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F14" s="24" t="s">
+      <x:c r="G14" s="6" t="s">
         <x:v>108</x:v>
-      </x:c>
-      <x:c r="G14" s="6" t="s">
-        <x:v>109</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1752,19 +1749,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C15" s="6" t="s">
-        <x:v>44</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D15" s="6" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E15" s="8" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F15" s="24" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="E15" s="8" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F15" s="24" t="s">
+      <x:c r="G15" s="6" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="G15" s="6" t="s">
-        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1775,19 +1772,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C16" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="D16" s="6" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="E16" s="6" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D16" s="6" t="s">
+      <x:c r="F16" s="24" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="E16" s="6" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="F16" s="24" t="s">
+      <x:c r="G16" s="6" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="G16" s="6" t="s">
-        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1798,19 +1795,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C17" s="12" t="s">
-        <x:v>38</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D17" s="6" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E17" s="6" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F17" s="24" t="s">
         <x:v>116</x:v>
       </x:c>
-      <x:c r="E17" s="6" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F17" s="24" t="s">
+      <x:c r="G17" s="6" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="G17" s="6" t="s">
-        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1821,19 +1818,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C18" s="6" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="D18" s="6" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E18" s="6" t="s">
         <x:v>34</x:v>
       </x:c>
-      <x:c r="D18" s="6" t="s">
-        <x:v>116</x:v>
-      </x:c>
-      <x:c r="E18" s="6" t="s">
-        <x:v>35</x:v>
-      </x:c>
       <x:c r="F18" s="24" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="G18" s="6" t="s">
         <x:v>119</x:v>
-      </x:c>
-      <x:c r="G18" s="6" t="s">
-        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -1844,19 +1841,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C19" s="6" t="s">
-        <x:v>54</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D19" s="6" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="E19" s="6" t="s">
         <x:v>121</x:v>
       </x:c>
-      <x:c r="E19" s="6" t="s">
+      <x:c r="F19" s="24" t="s">
         <x:v>122</x:v>
       </x:c>
-      <x:c r="F19" s="24" t="s">
+      <x:c r="G19" s="6" t="s">
         <x:v>123</x:v>
-      </x:c>
-      <x:c r="G19" s="6" t="s">
-        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -1867,19 +1864,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C20" s="6" t="s">
-        <x:v>49</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D20" s="6" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="E20" s="6" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="E20" s="6" t="s">
+      <x:c r="F20" s="24" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="F20" s="24" t="s">
+      <x:c r="G20" s="6" t="s">
         <x:v>127</x:v>
-      </x:c>
-      <x:c r="G20" s="6" t="s">
-        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -1890,19 +1887,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C21" s="6" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D21" s="6" t="s">
         <x:v>129</x:v>
       </x:c>
-      <x:c r="D21" s="6" t="s">
+      <x:c r="E21" s="6" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="F21" s="24" t="s">
         <x:v>130</x:v>
       </x:c>
-      <x:c r="E21" s="6" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="F21" s="24" t="s">
+      <x:c r="G21" s="6" t="s">
         <x:v>131</x:v>
-      </x:c>
-      <x:c r="G21" s="6" t="s">
-        <x:v>132</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -1913,19 +1910,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C22" s="6" t="s">
-        <x:v>60</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D22" s="6" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="E22" s="6" t="s">
         <x:v>133</x:v>
       </x:c>
-      <x:c r="E22" s="6" t="s">
+      <x:c r="F22" s="24" t="s">
         <x:v>134</x:v>
       </x:c>
-      <x:c r="F22" s="24" t="s">
+      <x:c r="G22" s="6" t="s">
         <x:v>135</x:v>
-      </x:c>
-      <x:c r="G22" s="6" t="s">
-        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -1936,19 +1933,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C23" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D23" s="6" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="E23" s="6" t="s">
         <x:v>137</x:v>
       </x:c>
-      <x:c r="E23" s="6" t="s">
+      <x:c r="F23" s="24" t="s">
         <x:v>138</x:v>
       </x:c>
-      <x:c r="F23" s="24" t="s">
+      <x:c r="G23" s="6" t="s">
         <x:v>139</x:v>
-      </x:c>
-      <x:c r="G23" s="6" t="s">
-        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -1959,19 +1956,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C24" s="6" t="s">
-        <x:v>52</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D24" s="26">
         <x:v>43922.0</x:v>
       </x:c>
       <x:c r="E24" s="6" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F24" s="24" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="G24" s="6" t="s">
         <x:v>141</x:v>
-      </x:c>
-      <x:c r="G24" s="6" t="s">
-        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -1982,19 +1979,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C25" s="6" t="s">
-        <x:v>62</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D25" s="26">
         <x:v>44805.0</x:v>
       </x:c>
       <x:c r="E25" s="6" t="s">
-        <x:v>126</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F25" s="24" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="G25" s="6" t="s">
         <x:v>143</x:v>
-      </x:c>
-      <x:c r="G25" s="6" t="s">
-        <x:v>144</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2005,19 +2002,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C26" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D26" s="6" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="E26" s="6" t="s">
         <x:v>145</x:v>
       </x:c>
-      <x:c r="E26" s="6" t="s">
+      <x:c r="F26" s="24" t="s">
         <x:v>146</x:v>
       </x:c>
-      <x:c r="F26" s="24" t="s">
+      <x:c r="G26" s="6" t="s">
         <x:v>147</x:v>
-      </x:c>
-      <x:c r="G26" s="6" t="s">
-        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2028,19 +2025,19 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C27" s="6" t="s">
-        <x:v>66</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D27" s="6" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="E27" s="6" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="F27" s="24" t="s">
         <x:v>149</x:v>
       </x:c>
-      <x:c r="E27" s="6" t="s">
-        <x:v>146</x:v>
-      </x:c>
-      <x:c r="F27" s="24" t="s">
+      <x:c r="G27" s="6" t="s">
         <x:v>150</x:v>
-      </x:c>
-      <x:c r="G27" s="6" t="s">
-        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2054,7 +2051,7 @@
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="17" t="s">
-        <x:v>152</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C29" s="2"/>
       <x:c r="D29" s="2"/>
@@ -2064,7 +2061,7 @@
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="17" t="s">
-        <x:v>153</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E30" s="2"/>
       <x:c r="F30" s="2"/>
